--- a/excel/Investavimas Gerda.xlsx
+++ b/excel/Investavimas Gerda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD04042-C48F-44CA-9B21-401F7AB126AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CB3340-6486-4510-B236-EC1E19960DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -596,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE7"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1006,14 +1006,14 @@
         <v>46265</v>
       </c>
       <c r="B6" s="11">
-        <v>200.31</v>
+        <v>350.31</v>
       </c>
       <c r="C6" s="12">
-        <v>242.56</v>
+        <v>392.56</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6" si="28">(C6-B6)/B6</f>
-        <v>0.21092306924267384</v>
+        <v>0.12060746196226199</v>
       </c>
       <c r="F6" s="4">
         <f>A6</f>
@@ -1032,15 +1032,15 @@
       </c>
       <c r="O6" s="2">
         <f t="shared" ref="O6" si="30">B6</f>
-        <v>200.31</v>
+        <v>350.31</v>
       </c>
       <c r="P6" s="2">
         <f t="shared" ref="P6" si="31">O6-O5</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="Q6" s="2">
         <f>C6</f>
-        <v>242.56</v>
+        <v>392.56</v>
       </c>
       <c r="R6" s="2">
         <f t="shared" ref="R6" si="32">Q6-O6</f>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="S6" s="7">
         <f t="shared" ref="S6" si="33">R6/O6</f>
-        <v>0.21092306924267384</v>
+        <v>0.12060746196226199</v>
       </c>
       <c r="T6" s="2">
         <f t="shared" ref="T6" si="34">R6-R5</f>
@@ -1061,15 +1061,15 @@
       </c>
       <c r="W6" s="2">
         <f t="shared" ref="W6" si="35">G6+O6</f>
-        <v>200.31</v>
+        <v>350.31</v>
       </c>
       <c r="X6" s="2">
         <f t="shared" ref="X6" si="36">W6-W5</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="Y6" s="2">
         <f t="shared" ref="Y6" si="37">I6+Q6</f>
-        <v>242.56</v>
+        <v>392.56</v>
       </c>
       <c r="Z6" s="2">
         <f t="shared" ref="Z6" si="38">Y6-W6</f>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="AA6" s="7">
         <f t="shared" ref="AA6" si="39">Z6/W6</f>
-        <v>0.21092306924267384</v>
+        <v>0.12060746196226199</v>
       </c>
       <c r="AB6" s="2">
         <f t="shared" ref="AB6" si="40">Z6-Z5</f>
@@ -1090,6 +1090,97 @@
       <c r="AE6" s="2">
         <f>(C6-B6)-(C5-B5)</f>
         <v>2.2599999999999909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>46295</v>
+      </c>
+      <c r="B7" s="11">
+        <v>350.31</v>
+      </c>
+      <c r="C7" s="12">
+        <v>395.61</v>
+      </c>
+      <c r="D7" s="13">
+        <f t="shared" ref="D7" si="41">(C7-B7)/B7</f>
+        <v>0.12931403613941941</v>
+      </c>
+      <c r="F7" s="4">
+        <f>A7</f>
+        <v>46295</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="4">
+        <f t="shared" ref="N7" si="42">A7</f>
+        <v>46295</v>
+      </c>
+      <c r="O7" s="2">
+        <f t="shared" ref="O7" si="43">B7</f>
+        <v>350.31</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" ref="P7" si="44">O7-O6</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <f>C7</f>
+        <v>395.61</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" ref="R7" si="45">Q7-O7</f>
+        <v>45.300000000000011</v>
+      </c>
+      <c r="S7" s="7">
+        <f t="shared" ref="S7" si="46">R7/O7</f>
+        <v>0.12931403613941941</v>
+      </c>
+      <c r="T7" s="2">
+        <f t="shared" ref="T7" si="47">R7-R6</f>
+        <v>3.0500000000000114</v>
+      </c>
+      <c r="U7" s="6"/>
+      <c r="V7" s="4">
+        <f>A7</f>
+        <v>46295</v>
+      </c>
+      <c r="W7" s="2">
+        <f t="shared" ref="W7" si="48">G7+O7</f>
+        <v>350.31</v>
+      </c>
+      <c r="X7" s="2">
+        <f t="shared" ref="X7" si="49">W7-W6</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <f t="shared" ref="Y7" si="50">I7+Q7</f>
+        <v>395.61</v>
+      </c>
+      <c r="Z7" s="2">
+        <f t="shared" ref="Z7" si="51">Y7-W7</f>
+        <v>45.300000000000011</v>
+      </c>
+      <c r="AA7" s="7">
+        <f t="shared" ref="AA7" si="52">Z7/W7</f>
+        <v>0.12931403613941941</v>
+      </c>
+      <c r="AB7" s="2">
+        <f t="shared" ref="AB7" si="53">Z7-Z6</f>
+        <v>3.0500000000000114</v>
+      </c>
+      <c r="AD7" s="4">
+        <f>A7</f>
+        <v>46295</v>
+      </c>
+      <c r="AE7" s="2">
+        <f>(C7-B7)-(C6-B6)</f>
+        <v>3.0500000000000114</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1196,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="X3:X6" formula="1"/>
+    <ignoredError sqref="X3:X7" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>